--- a/docs/PRJ301_SE20C_GROUP4 (1).xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276AA46C-C275-468A-9339-771DF584830E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE78EF-EC37-48EE-95BC-C0FF6E131E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="170">
   <si>
     <t>No.</t>
   </si>
@@ -521,13 +521,34 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1C72WWLyzh_2zq-OIQMlprdEkDgRMdWwf?usp=sharing</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Build UserConsoleTest.java to test DAO functions, Console Menu, Login/Register, CRUD, and role-based Admin/Student menus</t>
+  </si>
+  <si>
+    <t>Generated Console Test structure, Scanner-based menu, Login/Register/CRUD flow, and role-based menu handling</t>
+  </si>
+  <si>
+    <t>Tested and modified the generated code to match the project DAO and fixed Scanner input handling for invalid input</t>
+  </si>
+  <si>
+    <t>1 Test Suite, 8 business test scenarios</t>
+  </si>
+  <si>
+    <t>AI-generated code may not exactly match existing DAO methods; manually adjusted method calls and fixed Scanner.nextLine() buffer handling</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1-OKCkuc_DCyRqRFaBMpfMPzjAfGv7iIW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,51 +561,51 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -592,7 +613,14 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -694,7 +722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -768,16 +796,25 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1090,7 +1127,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="25" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="26"/>
@@ -1102,7 +1139,7 @@
       <c r="A3" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="28" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="26"/>
@@ -1113,7 +1150,7 @@
       <c r="A4" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="28" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="26"/>
@@ -1124,7 +1161,7 @@
       <c r="A5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="28" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="26"/>
@@ -1135,7 +1172,7 @@
       <c r="A6" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="28" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="26"/>
@@ -1146,7 +1183,7 @@
       <c r="A7" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="28" t="s">
         <v>35</v>
       </c>
       <c r="C7" s="26"/>
@@ -1157,7 +1194,7 @@
       <c r="A8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="28">
         <v>4</v>
       </c>
       <c r="C8" s="26"/>
@@ -1168,7 +1205,7 @@
       <c r="A9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="28" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="26"/>
@@ -1176,7 +1213,7 @@
       <c r="E9" s="27"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="29" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="26"/>
@@ -1288,6 +1325,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
@@ -1295,8 +1334,6 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2012,19 +2049,37 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" ht="82.8">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="B4" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="I4" s="7">
+        <v>5</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9">
@@ -2058,6 +2113,7 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{EB2E0BBB-C191-49CF-94F1-9B7CD811FA30}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{F30AC9DD-F5E5-4F9A-9CCD-6CFE9F77C925}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PRJ301_SE20C_GROUP4 (1).xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5530DD1-F78F-433A-AA3B-9A54503B4C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D53D640-2EC2-47EA-AA4E-7ACF485960E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="178">
   <si>
     <t>No.</t>
   </si>
@@ -542,13 +542,37 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1-OKCkuc_DCyRqRFaBMpfMPzjAfGv7iIW?usp=sharing</t>
+  </si>
+  <si>
+    <t>Implementation &amp; Database</t>
+  </si>
+  <si>
+    <t>Gemini, ChatGPT</t>
+  </si>
+  <si>
+    <t>AI suggested generic connection string with default port 1433 and wrong database name; lacked proper try-with-resources statement cleanup logic.</t>
+  </si>
+  <si>
+    <t>Configure JDBC database connection (DBContext.java) &amp; Build DAO layer (UserDAO.java) for AITA system</t>
+  </si>
+  <si>
+    <t>Provided DBContext source code configuring JDBC connection setup for SQL Server and basic CRUD methods in UserDAO.</t>
+  </si>
+  <si>
+    <t>Adjusted connection string parameters to localhost:1434/AITA_DB, fixed manual ResultSet/PreparedStatement resource leakage issues, and added SQLException handling (Error codes 2627, 547).</t>
+  </si>
+  <si>
+    <t>1 DBContext class, 1 UserDAO class (supporting 10 CRUD &amp; validation methods)</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -621,6 +645,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -722,7 +753,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -811,6 +842,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2078,19 +2115,37 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="124.2">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="B5" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" s="33">
+        <v>5</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9">
@@ -2111,6 +2166,7 @@
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{EB2E0BBB-C191-49CF-94F1-9B7CD811FA30}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{4D551FB5-D8EE-42B3-81F5-DF788EE246D4}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{7B6374D5-D446-4575-9225-FE0A7C7749D4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
